--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487624_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487624_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2341</v>
+        <v>3.6485</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4893</v>
+        <v>3.8492</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2552</v>
+        <v>-0.2007</v>
       </c>
       <c r="G2" t="n">
         <v>1.4826</v>
@@ -610,13 +610,13 @@
         <v>3.4926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5590000000000001</v>
+        <v>-0.0266</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5607</v>
+        <v>-0.0794</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0018</v>
+        <v>0.0527</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3299</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.962</v>
+        <v>3.1405</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4918</v>
+        <v>2.4523</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4702</v>
+        <v>0.6882</v>
       </c>
       <c r="G3" t="n">
         <v>-1.4248</v>
@@ -688,13 +688,13 @@
         <v>4.0747</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6297</v>
+        <v>-0.4512</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.47</v>
+        <v>-0.5095</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1597</v>
+        <v>0.0584</v>
       </c>
       <c r="V3" t="n">
         <v>0.9418</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. CUESTA DE SANTOS</t>
+          <t>R. LOPEZ RIVERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1079</v>
+        <v>2.4302</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1459</v>
+        <v>3.0225</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.038</v>
+        <v>-0.5923</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5251</v>
+        <v>3.0364</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6848</v>
+        <v>0.3798</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8403</v>
+        <v>2.6566</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6784</v>
+        <v>4.2164</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7425</v>
+        <v>1.0092</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9359</v>
+        <v>3.2071</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1533</v>
+        <v>-1.18</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0577</v>
+        <v>-0.6294</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0956</v>
+        <v>-0.5506</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1642</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1045</v>
+        <v>0.5821</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8185</v>
+        <v>-0.2181</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1839</v>
+        <v>-0.2238</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.0056</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.6238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. LOPEZ RIVERA</t>
+          <t>C. CUESTA DE SANTOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0059</v>
+        <v>1.4077</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7617</v>
+        <v>2.7455</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7558</v>
+        <v>-1.3378</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0364</v>
+        <v>2.5251</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3798</v>
+        <v>1.6848</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6566</v>
+        <v>0.8403</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2164</v>
+        <v>3.6784</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0092</v>
+        <v>1.7425</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2071</v>
+        <v>1.9359</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.18</v>
+        <v>-1.1533</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6294</v>
+        <v>-0.0577</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5506</v>
+        <v>-1.0956</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5821</v>
+        <v>3.1045</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6424</v>
+        <v>0.1183</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4845</v>
+        <v>-0.2165</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1579</v>
+        <v>0.3348</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-3.6238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. SANTANA DE LA ROSA</t>
+          <t>E. BOADA MONTESDEOCA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9371</v>
+        <v>0.7679</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-1.1951</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0028</v>
+        <v>1.963</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8639</v>
+        <v>-0.5866</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1808</v>
+        <v>1.7507</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3169</v>
+        <v>-2.3374</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0668</v>
+        <v>0.9957</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.5283</v>
+        <v>2.6323</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4615</v>
+        <v>-1.6366</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7971</v>
+        <v>-1.5823</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6525</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1446</v>
+        <v>-0.7008</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7463</v>
+        <v>0.7761</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7463</v>
+        <v>3.6866</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0547</v>
+        <v>-0.9275</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0011</v>
+        <v>-0.7863</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0536</v>
+        <v>-0.1413</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. BOADA MONTESDEOCA</t>
+          <t>H. SANTANA DE LA ROSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4348</v>
+        <v>0.7097</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2557</v>
+        <v>-0.2659</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6905</v>
+        <v>0.9755</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5866</v>
+        <v>-0.8639</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7507</v>
+        <v>-2.1808</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3374</v>
+        <v>1.3169</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9957</v>
+        <v>-0.0668</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6323</v>
+        <v>-1.5283</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.6366</v>
+        <v>1.4615</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5823</v>
+        <v>-0.7971</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.6525</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7008</v>
+        <v>-0.1446</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.6866</v>
+        <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2607</v>
+        <v>-0.1727</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8468</v>
+        <v>-0.1991</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4138</v>
+        <v>0.0264</v>
       </c>
       <c r="V7" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2716</v>
+        <v>-1.1715</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2391</v>
+        <v>-2.139</v>
       </c>
       <c r="F8" t="n">
         <v>0.9674</v>
@@ -1078,10 +1078,10 @@
         <v>1.1642</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5215</v>
+        <v>-0.4214</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2905</v>
+        <v>-0.1904</v>
       </c>
       <c r="U8" t="n">
         <v>-0.231</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5942</v>
+        <v>-3.1482</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8235</v>
+        <v>-2.323</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7708</v>
+        <v>-0.8253</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4835</v>
@@ -1156,13 +1156,13 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3033</v>
+        <v>0.1427</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5933</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2901</v>
+        <v>0.2355</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1657</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.57</v>
+        <v>-4.8454</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3409</v>
+        <v>-2.1802</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2291</v>
+        <v>-2.6652</v>
       </c>
       <c r="G10" t="n">
         <v>-1.963</v>
@@ -1234,13 +1234,13 @@
         <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3632</v>
+        <v>0.0878</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.424</v>
+        <v>-0.2633</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7871</v>
+        <v>0.3511</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2239</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.1746</v>
+        <v>-6.5651</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6783</v>
+        <v>-2.1778</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.4964</v>
+        <v>-4.3873</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3349</v>
@@ -1312,13 +1312,13 @@
         <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5576</v>
+        <v>0.0519</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6539</v>
+        <v>-0.1534</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.2053</v>
       </c>
       <c r="V11" t="n">
         <v>-3.3418</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.928600000000001</v>
+        <v>-3.625700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4855</v>
+        <v>1.788500000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.414400000000001</v>
+        <v>-5.414499999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9462999999999988</v>
@@ -1390,13 +1390,13 @@
         <v>20.3734</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.1198</v>
+        <v>-1.8168</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.0173</v>
+        <v>-2.7145</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8974</v>
+        <v>0.8975</v>
       </c>
       <c r="V12" t="n">
         <v>-6.6836</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.8358</v>
+        <v>7.1239</v>
       </c>
       <c r="E13" t="n">
-        <v>9.836</v>
+        <v>9.9361</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0002</v>
+        <v>-2.8122</v>
       </c>
       <c r="G13" t="n">
         <v>-0.2928</v>
@@ -1468,13 +1468,13 @@
         <v>1.9403</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0489</v>
+        <v>0.2392</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2894</v>
+        <v>-0.1893</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2405</v>
+        <v>0.4285</v>
       </c>
       <c r="V13" t="n">
         <v>6.4014</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1734</v>
+        <v>3.2975</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5268</v>
+        <v>1.3266</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6466</v>
+        <v>1.9709</v>
       </c>
       <c r="G14" t="n">
         <v>1.9265</v>
@@ -1546,13 +1546,13 @@
         <v>2.1344</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3336</v>
+        <v>0.4576</v>
       </c>
       <c r="T14" t="n">
-        <v>0.305</v>
+        <v>0.1048</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0285</v>
+        <v>0.3528</v>
       </c>
       <c r="V14" t="n">
         <v>1.8836</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>A. ARMSTRONG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0469</v>
+        <v>1.3424</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0788</v>
+        <v>1.7387</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1257</v>
+        <v>-0.3963</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0914</v>
+        <v>2.3484</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1755</v>
+        <v>1.16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2669</v>
+        <v>1.1884</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0536</v>
+        <v>4.6259</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0536</v>
+        <v>0.8404</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.7856</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0379</v>
+        <v>-2.2775</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.229</v>
+        <v>0.3196</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2669</v>
+        <v>-2.5971</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.3881</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1642</v>
+        <v>-2.3284</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1642</v>
+        <v>2.7164</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2375</v>
+        <v>-0.1702</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0318</v>
+        <v>-0.5589</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2057</v>
+        <v>0.3887</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. EBOLO OLU-ELIJAH</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4825</v>
+        <v>0.5008</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.0365</v>
+        <v>-0.6794</v>
       </c>
       <c r="F16" t="n">
-        <v>2.519</v>
+        <v>1.1802</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3858</v>
+        <v>0.0914</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8035</v>
+        <v>-0.1755</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4176</v>
+        <v>0.2669</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2666</v>
+        <v>0.0536</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2615</v>
+        <v>0.0536</v>
       </c>
       <c r="L16" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8808</v>
+        <v>0.0379</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4581</v>
+        <v>-0.229</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4227</v>
+        <v>0.2669</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7463</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.2687</v>
+        <v>-1.1642</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5224</v>
+        <v>1.1642</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8908</v>
+        <v>0.6914</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0134</v>
+        <v>0.4312</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8773</v>
+        <v>0.2602</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0478</v>
+        <v>-0.2821</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ARMSTRONG</t>
+          <t>D. EBOLO OLU-ELIJAH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3175</v>
+        <v>0.3707</v>
       </c>
       <c r="E17" t="n">
-        <v>1.038</v>
+        <v>-2.0365</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7205</v>
+        <v>2.4071</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3484</v>
+        <v>1.3858</v>
       </c>
       <c r="H17" t="n">
-        <v>1.16</v>
+        <v>1.8035</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1884</v>
+        <v>-0.4176</v>
       </c>
       <c r="J17" t="n">
-        <v>4.6259</v>
+        <v>2.2666</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8404</v>
+        <v>2.2615</v>
       </c>
       <c r="L17" t="n">
-        <v>3.7856</v>
+        <v>0.005</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2775</v>
+        <v>-0.8808</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3196</v>
+        <v>-0.4581</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.5971</v>
+        <v>-0.4227</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3881</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3284</v>
+        <v>-4.2687</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7164</v>
+        <v>2.5224</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1951</v>
+        <v>0.7789</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2596</v>
+        <v>0.0134</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0644</v>
+        <v>0.7655</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2239</v>
+        <v>-0.0478</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0756</v>
+        <v>0.1425</v>
       </c>
       <c r="E18" t="n">
         <v>1.0009</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0764</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3767</v>
@@ -1858,13 +1858,13 @@
         <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2429</v>
+        <v>0.461</v>
       </c>
       <c r="T18" t="n">
         <v>0.3645</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1216</v>
+        <v>0.0965</v>
       </c>
       <c r="V18" t="n">
         <v>0.2821</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>D. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7776</v>
+        <v>-1.1371</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1223</v>
+        <v>0.4212</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6553</v>
+        <v>-1.5584</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5414</v>
+        <v>0.2943</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0931</v>
+        <v>0.6129</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6345</v>
+        <v>-0.3187</v>
       </c>
       <c r="J19" t="n">
-        <v>0.725</v>
+        <v>2.0304</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4408</v>
+        <v>0.0412</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2842</v>
+        <v>1.9892</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2664</v>
+        <v>-1.7362</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3477</v>
+        <v>0.5718</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.9187</v>
+        <v>-2.3079</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3284</v>
+        <v>-1.1642</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1344</v>
+        <v>0.194</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0056</v>
+        <v>-0.4612</v>
       </c>
       <c r="T19" t="n">
-        <v>0.305</v>
+        <v>-0.445</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7006</v>
+        <v>-0.0162</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1761</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ALMENARA SANABRIAS</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2645</v>
+        <v>-1.1714</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3211</v>
+        <v>-0.3225</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5856</v>
+        <v>-0.8489</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2943</v>
+        <v>-1.5414</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6129</v>
+        <v>0.0931</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3187</v>
+        <v>-1.6345</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0304</v>
+        <v>0.725</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0412</v>
+        <v>0.4408</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9892</v>
+        <v>0.2842</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7362</v>
+        <v>-2.2664</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5718</v>
+        <v>-0.3477</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.3079</v>
+        <v>-1.9187</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1642</v>
+        <v>-2.3284</v>
       </c>
       <c r="R20" t="n">
-        <v>0.194</v>
+        <v>2.1344</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5886</v>
+        <v>0.6118</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5451</v>
+        <v>0.1048</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0435</v>
+        <v>0.507</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1761</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7393</v>
+        <v>-2.8572</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9925</v>
+        <v>-2.8924</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2533</v>
+        <v>0.0353</v>
       </c>
       <c r="G21" t="n">
         <v>0.7086</v>
@@ -2092,13 +2092,13 @@
         <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3268</v>
+        <v>0.2089</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4722</v>
+        <v>-0.3721</v>
       </c>
       <c r="U21" t="n">
-        <v>0.799</v>
+        <v>0.581</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2821</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0707</v>
+        <v>-3.0161</v>
       </c>
       <c r="E22" t="n">
         <v>-3.0784</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0078</v>
+        <v>0.0623</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5978</v>
@@ -2170,13 +2170,13 @@
         <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0848</v>
+        <v>-0.0303</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3511</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2663</v>
+        <v>0.3208</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.928399999999999</v>
+        <v>4.596</v>
       </c>
       <c r="E23" t="n">
         <v>5.414299999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4856</v>
+        <v>-0.8184000000000002</v>
       </c>
       <c r="G23" t="n">
         <v>0.9462999999999999</v>
@@ -2248,13 +2248,13 @@
         <v>14.5524</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1198</v>
+        <v>2.7871</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8976999999999997</v>
+        <v>-0.8976999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>3.0172</v>
+        <v>3.6848</v>
       </c>
       <c r="V23" t="n">
         <v>6.6834</v>
